--- a/ECOMMERCE APPLICATION FUNCTIONALITY SCENARIOS.xlsx
+++ b/ECOMMERCE APPLICATION FUNCTIONALITY SCENARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="622" documentId="8_{4A26E6FA-1D39-45BD-93BC-EBF93547C812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE90C230-73F4-4C86-B8BB-15AA7B9948F5}"/>
+  <xr:revisionPtr revIDLastSave="623" documentId="8_{4A26E6FA-1D39-45BD-93BC-EBF93547C812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80572561-4A54-48D8-845A-E59EB2D07289}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{7D877A49-2E6C-4183-957F-DE36F0A3DC42}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="426">
   <si>
     <t>APPLICATION NAME</t>
   </si>
@@ -4548,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F6E4C7-A06B-45BD-B7AF-93660937DFFC}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
@@ -5573,6 +5573,16 @@
       </c>
       <c r="D84" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
